--- a/results/link-prediction-gcn/Link/0shot/Cora/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/Cora/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.5225±0.0172</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.5531±0.0751</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4779±0.0062</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5032±0.0107</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4820±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5610±0.0863</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0050</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0050</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0050</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.7223±0.0164</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.7075±0.0224</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.7441±0.0180</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5361±0.0510</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.6515±0.1091</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.5149±0.0254</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5326±0.0220</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.7489±0.0078</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6518±0.1073</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.6518±0.1073</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.6518±0.1073</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.7438±0.0151</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.7321±0.0111</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5737±0.1042</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5231±0.0326</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5104±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5104±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5104±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.5455±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5560±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.6205±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4911±0.0132</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5120±0.0170</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4687±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.5028±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6657±0.0065</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.7657±0.0114</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.7657±0.0114</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.7657±0.0114</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.6097±0.0776</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.7302±0.0091</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.7644±0.0101</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6727±0.0752</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4848±0.0039</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5446±0.0222</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.7296±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.7470±0.0072</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.7423±0.0144</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.7423±0.0144</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7423±0.0144</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.7369±0.0067</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.7125±0.0041</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7429±0.0151</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5319±0.0452</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5547±0.0774</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5003±0.0035</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4934±0.0074</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.7552±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.7419±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5557±0.0787</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.7448±0.0020</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7448±0.0020</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7448±0.0020</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5563±0.0796</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6120±0.0190</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.7568±0.0040</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.5174±0.0373</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.5481±0.0680</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4905±0.0128</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.5370±0.0300</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.6578±0.1117</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.7359±0.0098</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.7479±0.0100</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.6066±0.0762</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.6436±0.0931</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.7568±0.0029</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4696±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.7207±0.0106</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.5101±0.0029</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5389±0.0128</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.5342±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.5342±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.5342±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.6698±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.5370±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5351±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4943±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4801±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.7343±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6964±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6964±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6964±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.7287±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6660±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.6973±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4668±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4981±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5342±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5342±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5342±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.6214±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4972±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5123±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5009±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4867±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4820±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.7097±0.0000</t>
+          <t>0.7138±0.0057</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5098±0.0019</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5098±0.0019</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5098±0.0019</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5753±0.0850</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5550±0.0000</t>
+          <t>0.5961±0.0446</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5139±0.0037</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.6271±0.0315</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.6802±0.0192</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.6407±0.0050</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6528±0.0111</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6654±0.0000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6500±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6889±0.0314</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6715±0.0027</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6715±0.0027</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6715±0.0027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.7679±0.0122</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.7551±0.0171</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7868±0.0134</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6257±0.0580</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.7410±0.0543</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6521±0.0047</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6621±0.0084</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7928±0.0049</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7414±0.0528</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.7414±0.0528</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7414±0.0528</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7901±0.0109</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7793±0.0078</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.7032±0.0517</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.3297±0.2722</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.6701±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.6701±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.6701±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.6842±0.0000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6176±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7171±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6552±0.0165</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6634±0.0043</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6340±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6530±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.7145±0.0069</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.8059±0.0084</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.8059±0.0084</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.8059±0.0084</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6990±0.0233</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7764±0.0063</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.8054±0.0069</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7492±0.0376</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6434±0.0073</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6622±0.0156</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.7806±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7910±0.0040</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7875±0.0105</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7875±0.0105</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7875±0.0105</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7846±0.0043</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7649±0.0034</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7884±0.0112</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6441±0.0320</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6809±0.0201</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6657±0.0018</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6597±0.0078</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.7991±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7872±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6838±0.0242</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7887±0.0021</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7887±0.0021</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7887±0.0021</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6846±0.0254</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7180±0.0101</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7983±0.0026</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.5553±0.1431</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0147</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6564±0.0140</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6585±0.0126</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.7443±0.0551</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.7833±0.0063</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.7912±0.0074</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6963±0.0236</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.7283±0.0409</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.7984±0.0029</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6339±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.7698±0.0079</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6496±0.0033</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6669±0.0035</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.6814±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.6814±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.6814±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.7434±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6831±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6826±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6612±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6451±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7853±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7615±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7615±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7615±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7810±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7457±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7625±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6312±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6646±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6814±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6814±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6814±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7239±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6658±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6641±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6714±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6671±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6525±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6360±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7609±0.0000</t>
+          <t>0.7647±0.0029</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6701±0.0016</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6701±0.0016</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6701±0.0016</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6980±0.0353</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6908±0.0000</t>
+          <t>0.7033±0.0155</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6725±0.0019</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.5568±0.0000</t>
+          <t>0.5903±0.0053</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6814±0.0000</t>
+          <t>0.6927±0.0280</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5996±0.0000</t>
+          <t>0.6307±0.0145</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6467±0.0000</t>
+          <t>0.6581±0.0078</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6722±0.0000</t>
+          <t>0.6831±0.0080</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6775±0.0000</t>
+          <t>0.6788±0.0137</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.7113±0.0483</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.7491±0.0100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.7491±0.0100</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7411±0.0000</t>
+          <t>0.7491±0.0100</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6867±0.0000</t>
+          <t>0.8292±0.0000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6145±0.0000</t>
+          <t>0.8270±0.0230</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7731±0.0000</t>
+          <t>0.8767±0.0077</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5918±0.0000</t>
+          <t>0.5782±0.0143</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7567±0.0000</t>
+          <t>0.8382±0.0607</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4802±0.0000</t>
+          <t>0.6196±0.0341</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6377±0.0000</t>
+          <t>0.6593±0.0160</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6648±0.0000</t>
+          <t>0.6635±0.0088</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6531±0.0000</t>
+          <t>0.6610±0.0044</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.8814±0.0000</t>
+          <t>0.9025±0.0062</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8105±0.0000</t>
+          <t>0.8564±0.0404</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.8105±0.0000</t>
+          <t>0.8564±0.0404</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.8105±0.0000</t>
+          <t>0.8564±0.0404</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8931±0.0000</t>
+          <t>0.8923±0.0062</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8684±0.0000</t>
+          <t>0.8492±0.0120</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7978±0.0000</t>
+          <t>0.8121±0.0484</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5952±0.0000</t>
+          <t>0.5900±0.0025</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6781±0.0000</t>
+          <t>0.6832±0.0123</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6369±0.0000</t>
+          <t>0.6463±0.0122</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6481±0.0000</t>
+          <t>0.6493±0.0129</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6739±0.0000</t>
+          <t>0.6810±0.0071</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6735±0.0000</t>
+          <t>0.6812±0.0095</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.6838±0.0000</t>
+          <t>0.7570±0.0054</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.8728±0.0000</t>
+          <t>0.9300±0.0067</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.8728±0.0000</t>
+          <t>0.9300±0.0067</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.8728±0.0000</t>
+          <t>0.9300±0.0067</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.6743±0.0000</t>
+          <t>0.7456±0.0243</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8562±0.0000</t>
+          <t>0.8776±0.0049</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.8698±0.0000</t>
+          <t>0.9347±0.0060</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5537±0.0000</t>
+          <t>0.5557±0.0240</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7631±0.0000</t>
+          <t>0.8614±0.0315</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4812±0.0000</t>
+          <t>0.6366±0.0133</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4830±0.0000</t>
+          <t>0.6781±0.0202</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6809±0.0000</t>
+          <t>0.6881±0.0261</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6520±0.0000</t>
+          <t>0.6771±0.0076</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8931±0.0000</t>
+          <t>0.8919±0.0122</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8635±0.0000</t>
+          <t>0.8994±0.0137</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8635±0.0000</t>
+          <t>0.8994±0.0137</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8635±0.0000</t>
+          <t>0.8994±0.0137</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8891±0.0000</t>
+          <t>0.8807±0.0110</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8816±0.0000</t>
+          <t>0.8583±0.0104</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8562±0.0000</t>
+          <t>0.9005±0.0125</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.5157±0.0000</t>
+          <t>0.6192±0.0348</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6838±0.0000</t>
+          <t>0.7013±0.0186</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.6290±0.0000</t>
+          <t>0.6329±0.0283</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6603±0.0000</t>
+          <t>0.6439±0.0144</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6626±0.0000</t>
+          <t>0.6630±0.0055</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6666±0.0000</t>
+          <t>0.6803±0.0096</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6868±0.0000</t>
+          <t>0.7114±0.0241</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.8323±0.0000</t>
+          <t>0.8867±0.0069</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.8323±0.0000</t>
+          <t>0.8867±0.0069</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.8323±0.0000</t>
+          <t>0.8867±0.0069</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6867±0.0000</t>
+          <t>0.7048±0.0311</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8399±0.0000</t>
+          <t>0.8279±0.0093</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.8290±0.0000</t>
+          <t>0.8964±0.0021</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.6012±0.0000</t>
+          <t>0.6411±0.0038</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6920±0.0000</t>
+          <t>0.6904±0.0121</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6451±0.0000</t>
+          <t>0.6323±0.0090</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6412±0.0000</t>
+          <t>0.6437±0.0304</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.6681±0.0055</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6722±0.0000</t>
+          <t>0.6718±0.0018</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6967±0.0000</t>
+          <t>0.6939±0.0118</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7643±0.0000</t>
+          <t>0.8455±0.0666</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7643±0.0000</t>
+          <t>0.8963±0.0094</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7643±0.0000</t>
+          <t>0.9013±0.0107</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6883±0.0000</t>
+          <t>0.7307±0.0280</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.8369±0.0000</t>
+          <t>0.8474±0.0074</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7939±0.0000</t>
+          <t>0.9045±0.0058</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5748±0.0000</t>
+          <t>0.5973±0.0325</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7881±0.0000</t>
+          <t>0.8466±0.0106</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4857±0.0000</t>
+          <t>0.6298±0.0207</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5922±0.0000</t>
+          <t>0.6818±0.0173</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6724±0.0000</t>
+          <t>0.6693±0.0090</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.6337±0.0000</t>
+          <t>0.6504±0.0149</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.8317±0.0000</t>
+          <t>0.8540±0.0085</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7904±0.0000</t>
+          <t>0.7672±0.0195</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7904±0.0000</t>
+          <t>0.7672±0.0195</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7904±0.0000</t>
+          <t>0.7672±0.0195</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7984±0.0000</t>
+          <t>0.8053±0.0144</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.8081±0.0000</t>
+          <t>0.7742±0.0187</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7787±0.0000</t>
+          <t>0.7469±0.0245</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.5771±0.0000</t>
+          <t>0.6119±0.0105</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7163±0.0000</t>
+          <t>0.7167±0.0232</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5893±0.0000</t>
+          <t>0.6856±0.0154</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6930±0.0000</t>
+          <t>0.7010±0.0073</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7053±0.0000</t>
+          <t>0.7102±0.0047</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7095±0.0000</t>
+          <t>0.7031±0.0109</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7192±0.0000</t>
+          <t>0.7379±0.0327</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7523±0.0000</t>
+          <t>0.7533±0.0065</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7523±0.0000</t>
+          <t>0.7533±0.0065</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7523±0.0000</t>
+          <t>0.7533±0.0065</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7236±0.0000</t>
+          <t>0.8292±0.0040</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6465±0.0000</t>
+          <t>0.8269±0.0238</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7546±0.0000</t>
+          <t>0.8746±0.0122</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6616±0.0000</t>
+          <t>0.6401±0.0122</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7748±0.0000</t>
+          <t>0.8396±0.0480</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.4905±0.0000</t>
+          <t>0.6357±0.0553</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.6128±0.0000</t>
+          <t>0.6751±0.0272</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6962±0.0000</t>
+          <t>0.6925±0.0123</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6974±0.0000</t>
+          <t>0.6863±0.0073</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8693±0.0000</t>
+          <t>0.8993±0.0051</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8040±0.0000</t>
+          <t>0.8451±0.0538</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8040±0.0000</t>
+          <t>0.8451±0.0538</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.8040±0.0000</t>
+          <t>0.8451±0.0538</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8838±0.0000</t>
+          <t>0.8853±0.0084</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8456±0.0000</t>
+          <t>0.8202±0.0172</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7872±0.0000</t>
+          <t>0.7982±0.0531</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6358±0.0000</t>
+          <t>0.6250±0.0044</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7231±0.0000</t>
+          <t>0.7255±0.0037</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6474±0.0000</t>
+          <t>0.6882±0.0206</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6995±0.0000</t>
+          <t>0.7012±0.0093</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7057±0.0000</t>
+          <t>0.7052±0.0018</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7034±0.0000</t>
+          <t>0.7090±0.0069</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7308±0.0000</t>
+          <t>0.7604±0.0079</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.8761±0.0000</t>
+          <t>0.9312±0.0069</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.8761±0.0000</t>
+          <t>0.9312±0.0069</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.8761±0.0000</t>
+          <t>0.9312±0.0069</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7243±0.0000</t>
+          <t>0.7640±0.0107</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8679±0.0000</t>
+          <t>0.8830±0.0067</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.8715±0.0000</t>
+          <t>0.9356±0.0077</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5997±0.0000</t>
+          <t>0.6022±0.0204</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7642±0.0000</t>
+          <t>0.8624±0.0330</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4906±0.0000</t>
+          <t>0.6865±0.0163</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4917±0.0000</t>
+          <t>0.7049±0.0176</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.7146±0.0000</t>
+          <t>0.7107±0.0211</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6970±0.0000</t>
+          <t>0.7009±0.0053</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8949±0.0000</t>
+          <t>0.8918±0.0137</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8590±0.0000</t>
+          <t>0.9031±0.0141</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8590±0.0000</t>
+          <t>0.9031±0.0141</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8590±0.0000</t>
+          <t>0.9031±0.0141</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8896±0.0000</t>
+          <t>0.8787±0.0152</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8753±0.0000</t>
+          <t>0.8581±0.0154</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8459±0.0000</t>
+          <t>0.9017±0.0134</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.5807±0.0000</t>
+          <t>0.6435±0.0310</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7167±0.0000</t>
+          <t>0.7207±0.0185</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6335±0.0000</t>
+          <t>0.6862±0.0255</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7133±0.0000</t>
+          <t>0.7045±0.0075</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6917±0.0000</t>
+          <t>0.6896±0.0078</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6996±0.0000</t>
+          <t>0.7055±0.0052</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7193±0.0000</t>
+          <t>0.7328±0.0127</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.8235±0.0000</t>
+          <t>0.8869±0.0076</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.8235±0.0000</t>
+          <t>0.8869±0.0076</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.8235±0.0000</t>
+          <t>0.8869±0.0076</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7248±0.0000</t>
+          <t>0.7268±0.0235</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8226±0.0000</t>
+          <t>0.8068±0.0115</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8279±0.0000</t>
+          <t>0.8964±0.0028</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6694±0.0000</t>
+          <t>0.6624±0.0137</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.7090±0.0117</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6895±0.0000</t>
+          <t>0.6885±0.0035</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6758±0.0000</t>
+          <t>0.6800±0.0356</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7018±0.0000</t>
+          <t>0.7015±0.0066</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7044±0.0000</t>
+          <t>0.6961±0.0068</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7258±0.0000</t>
+          <t>0.7219±0.0048</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7840±0.0000</t>
+          <t>0.8497±0.0577</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7840±0.0000</t>
+          <t>0.8989±0.0083</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7840±0.0000</t>
+          <t>0.9005±0.0108</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7197±0.0000</t>
+          <t>0.7486±0.0170</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.8556±0.0000</t>
+          <t>0.8616±0.0050</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.9019±0.0078</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6172±0.0000</t>
+          <t>0.6251±0.0252</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.8017±0.0000</t>
+          <t>0.8474±0.0125</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4929±0.0000</t>
+          <t>0.6412±0.0348</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5703±0.0000</t>
+          <t>0.6811±0.0277</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7022±0.0000</t>
+          <t>0.6936±0.0101</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6692±0.0000</t>
+          <t>0.6716±0.0086</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.8283±0.0000</t>
+          <t>0.8603±0.0115</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.7518±0.0132</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.7518±0.0132</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.7518±0.0132</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7992±0.0000</t>
+          <t>0.7970±0.0276</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.8015±0.0000</t>
+          <t>0.7638±0.0180</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7568±0.0000</t>
+          <t>0.7175±0.0185</t>
         </is>
       </c>
     </row>
